--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/mar-2026.xlsx
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25670150.45</v>
+        <v>28212.27</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>16247835</v>
+        <v>17856.86</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>36798987.26</v>
+        <v>40443.19</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12497027.62</v>
+        <v>13734.61</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>16080169.95</v>
+        <v>17672.59</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9548560</v>
+        <v>10494.15</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25523993.8</v>
+        <v>28051.64</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7796398.9</v>
+        <v>8568.48</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10623249</v>
+        <v>11675.27</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8152690</v>
+        <v>8960.049999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9545425.199999999</v>
+        <v>10490.71</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15109764.69</v>
+        <v>16606.09</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10835308.8</v>
+        <v>11908.33</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>39274129.3</v>
+        <v>43163.45</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>10837339.8</v>
+        <v>11910.56</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>10343751.15</v>
+        <v>11368.09</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>36845084.3</v>
+        <v>40493.86</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17689044</v>
+        <v>19440.79</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>18446219.75</v>
+        <v>20272.95</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7994434.45</v>
+        <v>8786.120000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>20976674</v>
+        <v>23054</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>9071436.300000001</v>
+        <v>9969.780000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>20213369.26</v>
+        <v>22215.1</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>40441237.62</v>
+        <v>44446.14</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>25686192</v>
+        <v>28229.9</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>37234496.5</v>
+        <v>40921.83</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>27388737.4</v>
+        <v>30101.05</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>33986522.4</v>
+        <v>37352.21</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8079862</v>
+        <v>8880.01</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5029394.75</v>
+        <v>5527.46</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5496560.7</v>
+        <v>6040.89</v>
       </c>
     </row>
     <row r="33">
@@ -2456,11 +2456,11 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>47491569.75</v>
+        <v>52194.66</v>
       </c>
     </row>
     <row r="34">
@@ -2517,11 +2517,11 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>11691928.5</v>
+        <v>12849.78</v>
       </c>
     </row>
     <row r="35">
@@ -2578,11 +2578,11 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>22257014.22</v>
+        <v>24461.13</v>
       </c>
     </row>
     <row r="36">
@@ -2639,11 +2639,11 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>17414313.84</v>
+        <v>19138.85</v>
       </c>
     </row>
     <row r="37">
@@ -2700,11 +2700,11 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12131931</v>
+        <v>13333.36</v>
       </c>
     </row>
     <row r="38">
@@ -2761,11 +2761,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6728878.8</v>
+        <v>7395.24</v>
       </c>
     </row>
     <row r="39">
@@ -2822,11 +2822,11 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>19542244.68</v>
+        <v>21477.51</v>
       </c>
     </row>
     <row r="40">
@@ -2883,11 +2883,11 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>7858688.6</v>
+        <v>8636.940000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2944,11 +2944,11 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12612280</v>
+        <v>13861.28</v>
       </c>
     </row>
     <row r="42">
@@ -3005,11 +3005,11 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>11439598.92</v>
+        <v>12572.46</v>
       </c>
     </row>
   </sheetData>
